--- a/data/availability/projects/emaar-misr/mivida.xlsx
+++ b/data/availability/projects/emaar-misr/mivida.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mivida</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2022</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1197,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1247,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1297,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1347,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1397,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1497,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1547,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1659,7 +1669,6 @@
       <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1670,7 +1679,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2022</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1716,7 +1725,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1727,7 +1735,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1773,7 +1781,6 @@
       <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1784,7 +1791,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1830,7 +1837,6 @@
       <c r="G5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1841,7 +1847,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1887,7 +1893,6 @@
       <c r="G6" t="n">
         <v>120</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1944,7 +1949,6 @@
       <c r="G7" t="n">
         <v>120</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1955,7 +1959,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2001,7 +2005,6 @@
       <c r="G8" t="n">
         <v>120</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2012,7 +2015,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2058,7 +2061,6 @@
       <c r="G9" t="n">
         <v>120</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2069,7 +2071,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2115,7 +2117,6 @@
       <c r="G10" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2126,7 +2127,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2172,7 +2173,6 @@
       <c r="G11" t="n">
         <v>120</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2229,7 +2229,6 @@
       <c r="G12" t="n">
         <v>120</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2240,7 +2239,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2286,7 +2285,6 @@
       <c r="G13" t="n">
         <v>120</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2297,7 +2295,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2343,7 +2341,6 @@
       <c r="G14" t="n">
         <v>120</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2354,7 +2351,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2400,7 +2397,6 @@
       <c r="G15" t="n">
         <v>120</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2411,7 +2407,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2457,7 +2453,6 @@
       <c r="G16" t="n">
         <v>120</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2468,7 +2463,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2514,7 +2509,6 @@
       <c r="G17" t="n">
         <v>120</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2525,7 +2519,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2571,7 +2565,6 @@
       <c r="G18" t="n">
         <v>120</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2582,7 +2575,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2628,7 +2621,6 @@
       <c r="G19" t="n">
         <v>120</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2639,7 +2631,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2685,7 +2677,6 @@
       <c r="G20" t="n">
         <v>120</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2696,7 +2687,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2742,7 +2733,6 @@
       <c r="G21" t="n">
         <v>120</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2753,7 +2743,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2799,7 +2789,6 @@
       <c r="G22" t="n">
         <v>120</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2810,7 +2799,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2856,7 +2845,6 @@
       <c r="G23" t="n">
         <v>120</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2867,7 +2855,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2913,7 +2901,6 @@
       <c r="G24" t="n">
         <v>120</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2924,7 +2911,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2970,7 +2957,6 @@
       <c r="G25" t="n">
         <v>120</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2981,7 +2967,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3027,7 +3013,6 @@
       <c r="G26" t="n">
         <v>120</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3038,7 +3023,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3084,7 +3069,6 @@
       <c r="G27" t="n">
         <v>164</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3095,7 +3079,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3141,7 +3125,6 @@
       <c r="G28" t="n">
         <v>278.6</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3152,7 +3135,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3198,7 +3181,6 @@
       <c r="G29" t="n">
         <v>315.6</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3209,7 +3191,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3255,7 +3237,6 @@
       <c r="G30" t="n">
         <v>274.9</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3266,7 +3247,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3312,7 +3293,6 @@
       <c r="G31" t="n">
         <v>248.6</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3323,7 +3303,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3369,7 +3349,6 @@
       <c r="G32" t="n">
         <v>455.2</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3380,7 +3359,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3426,7 +3405,6 @@
       <c r="G33" t="n">
         <v>326.9</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3437,7 +3415,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3483,7 +3461,6 @@
       <c r="G34" t="n">
         <v>673.6</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3494,7 +3471,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3540,7 +3517,6 @@
       <c r="G35" t="n">
         <v>416</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3551,7 +3527,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31/05/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3597,7 +3573,6 @@
       <c r="G36" t="n">
         <v>415.8</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3608,7 +3583,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3654,7 +3629,6 @@
       <c r="G37" t="n">
         <v>344.3</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3665,7 +3639,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3711,7 +3685,6 @@
       <c r="G38" t="n">
         <v>419.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3722,7 +3695,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3768,7 +3741,6 @@
       <c r="G39" t="n">
         <v>519.1</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3779,7 +3751,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3825,7 +3797,6 @@
       <c r="G40" t="n">
         <v>659.4</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3836,7 +3807,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3882,7 +3853,6 @@
       <c r="G41" t="n">
         <v>787.6</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3893,7 +3863,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3939,7 +3909,6 @@
       <c r="G42" t="n">
         <v>740.3</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3950,7 +3919,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3996,7 +3965,6 @@
       <c r="G43" t="n">
         <v>697.4</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4007,7 +3975,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4053,7 +4021,6 @@
       <c r="G44" t="n">
         <v>674.2</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4064,7 +4031,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4110,7 +4077,6 @@
       <c r="G45" t="n">
         <v>409.7</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4121,7 +4087,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4167,7 +4133,6 @@
       <c r="G46" t="n">
         <v>523</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4178,7 +4143,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4224,7 +4189,6 @@
       <c r="G47" t="n">
         <v>469.2</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4235,7 +4199,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4281,7 +4245,6 @@
       <c r="G48" t="n">
         <v>433.7</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4292,7 +4255,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4338,7 +4301,6 @@
       <c r="G49" t="n">
         <v>485.4</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4349,7 +4311,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4395,7 +4357,6 @@
       <c r="G50" t="n">
         <v>593.2</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4406,7 +4367,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4452,7 +4413,6 @@
       <c r="G51" t="n">
         <v>420.8</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4463,7 +4423,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4509,7 +4469,6 @@
       <c r="G52" t="n">
         <v>413.8</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4520,7 +4479,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4566,7 +4525,6 @@
       <c r="G53" t="n">
         <v>827.2</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4577,7 +4535,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4623,7 +4581,6 @@
       <c r="G54" t="n">
         <v>477.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4634,7 +4591,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>30/11/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4680,7 +4637,6 @@
       <c r="G55" t="n">
         <v>120</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4691,7 +4647,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4737,7 +4693,6 @@
       <c r="G56" t="n">
         <v>120</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4748,7 +4703,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4794,7 +4749,6 @@
       <c r="G57" t="n">
         <v>120</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4805,7 +4759,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4851,7 +4805,6 @@
       <c r="G58" t="n">
         <v>120</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4862,7 +4815,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4908,7 +4861,6 @@
       <c r="G59" t="n">
         <v>120</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4919,7 +4871,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4965,7 +4917,6 @@
       <c r="G60" t="n">
         <v>120</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4976,7 +4927,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5022,7 +4973,6 @@
       <c r="G61" t="n">
         <v>120</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5033,7 +4983,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5079,7 +5029,6 @@
       <c r="G62" t="n">
         <v>120</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5090,7 +5039,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5136,7 +5085,6 @@
       <c r="G63" t="n">
         <v>120</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5147,7 +5095,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5193,7 +5141,6 @@
       <c r="G64" t="n">
         <v>120</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5204,7 +5151,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5250,7 +5197,6 @@
       <c r="G65" t="n">
         <v>120</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5261,7 +5207,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5307,7 +5253,6 @@
       <c r="G66" t="n">
         <v>120</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5318,7 +5263,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5364,7 +5309,6 @@
       <c r="G67" t="n">
         <v>120</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5375,7 +5319,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5421,7 +5365,6 @@
       <c r="G68" t="n">
         <v>120</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5432,7 +5375,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5478,7 +5421,6 @@
       <c r="G69" t="n">
         <v>120</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5489,7 +5431,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5535,7 +5477,6 @@
       <c r="G70" t="n">
         <v>120</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5546,7 +5487,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5592,7 +5533,6 @@
       <c r="G71" t="n">
         <v>120</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5603,7 +5543,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5649,7 +5589,6 @@
       <c r="G72" t="n">
         <v>323.3</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5660,7 +5599,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5706,7 +5645,6 @@
       <c r="G73" t="n">
         <v>226.5</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5717,7 +5655,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5763,7 +5701,6 @@
       <c r="G74" t="n">
         <v>224.8</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5774,7 +5711,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5820,7 +5757,6 @@
       <c r="G75" t="n">
         <v>332.3</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5831,7 +5767,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5877,7 +5813,6 @@
       <c r="G76" t="n">
         <v>314.1</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5888,7 +5823,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5934,7 +5869,6 @@
       <c r="G77" t="n">
         <v>216.7</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5945,7 +5879,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5991,7 +5925,6 @@
       <c r="G78" t="n">
         <v>215.6</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6002,7 +5935,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6048,7 +5981,6 @@
       <c r="G79" t="n">
         <v>216.7</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6059,7 +5991,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6105,7 +6037,6 @@
       <c r="G80" t="n">
         <v>217.6</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6116,7 +6047,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6162,7 +6093,6 @@
       <c r="G81" t="n">
         <v>215.1</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6173,7 +6103,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6219,7 +6149,6 @@
       <c r="G82" t="n">
         <v>322.7</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6230,7 +6159,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6276,7 +6205,6 @@
       <c r="G83" t="n">
         <v>220.8</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6287,7 +6215,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6333,7 +6261,6 @@
       <c r="G84" t="n">
         <v>221.1</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6344,7 +6271,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6390,7 +6317,6 @@
       <c r="G85" t="n">
         <v>317</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6401,7 +6327,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6447,7 +6373,6 @@
       <c r="G86" t="n">
         <v>314</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6458,7 +6383,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6504,7 +6429,6 @@
       <c r="G87" t="n">
         <v>217.4</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6515,7 +6439,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6561,7 +6485,6 @@
       <c r="G88" t="n">
         <v>218.6</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6572,7 +6495,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6618,7 +6541,6 @@
       <c r="G89" t="n">
         <v>330</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6629,7 +6551,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>31/01/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
